--- a/FPSDemo/MiniTemplate/Datas/#enemy_config.xlsx
+++ b/FPSDemo/MiniTemplate/Datas/#enemy_config.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemy_config" sheetId="1" r:id="R037e20ce40af4201"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemy_config" sheetId="1" r:id="R4426439d1ae34962"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -904,13 +904,13 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="L6" s="2" t="n">
-        <x:v>2.45</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="M6" s="2" t="n">
         <x:v>420</x:v>
       </x:c>
       <x:c r="N6" s="2" t="n">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="O6" s="2" t="n">
         <x:v>9</x:v>
@@ -1024,7 +1024,7 @@
         <x:v>ZombieBasicDrop</x:v>
       </x:c>
       <x:c r="K7" s="2" t="n">
-        <x:v>180</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="L7" s="2" t="n">
         <x:v>1.45</x:v>
@@ -1036,7 +1036,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="O7" s="2" t="n">
-        <x:v>14</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="P7" s="2" t="n">
         <x:v>1.45</x:v>
